--- a/e2e/downloadedFile/sub_Master_Prorate_Others.xlsx
+++ b/e2e/downloadedFile/sub_Master_Prorate_Others.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="28">
   <si>
     <t>DAFTAR PEMBAYARAN GAJI LAIN-LAIN</t>
   </si>
@@ -56,54 +56,15 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>DE JESUS</t>
+    <t>RIMBUN SIBURIAN</t>
   </si>
   <si>
     <t>Local</t>
   </si>
   <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>1 sampai dengan 12 january</t>
-  </si>
-  <si>
-    <t>$ 12.00</t>
-  </si>
-  <si>
-    <t>$ 1.94</t>
-  </si>
-  <si>
-    <t>$ 23.28</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>AHMAD RIYANA SAPUTRA</t>
-  </si>
-  <si>
-    <t>Expat</t>
-  </si>
-  <si>
     <t>IV</t>
   </si>
   <si>
-    <t>cek</t>
-  </si>
-  <si>
-    <t>$ 1.00</t>
-  </si>
-  <si>
-    <t>$ 16.13</t>
-  </si>
-  <si>
-    <t>test 2</t>
-  </si>
-  <si>
-    <t>RIMBUN SIBURIAN</t>
-  </si>
-  <si>
     <t>Taxi online claim</t>
   </si>
   <si>
@@ -119,10 +80,7 @@
     <t>Remark taxi online claim updated</t>
   </si>
   <si>
-    <t>$ 64.41</t>
-  </si>
-  <si>
-    <t>DILI, 14 AGUSTUS 2026</t>
+    <t>DILI, 18 AGUSTUS 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
@@ -233,7 +191,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="514350" cy="333375"/>
@@ -552,16 +510,16 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="true" style="0"/>
     <col min="2" max="2" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="24.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="18.71" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="31.707" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="21.138" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="8" max="8" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="9.283" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="38.848" bestFit="true" customWidth="true" style="0"/>
@@ -622,7 +580,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="3">
-        <v>83008</v>
+        <v>81010</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>13</v>
@@ -650,125 +608,61 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="3">
-        <v>2</v>
-      </c>
-      <c r="B7" s="3">
-        <v>95008</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E9"/>
+      <c r="H9"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E10"/>
+      <c r="H10" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="3">
-        <v>3</v>
-      </c>
-      <c r="B8" s="3">
-        <v>81010</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>35</v>
-      </c>
+    </row>
+    <row r="11" spans="1:10" customHeight="1" ht="37.5">
+      <c r="A11"/>
       <c r="E11"/>
       <c r="H11"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>36</v>
+      <c r="A12" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="E12"/>
-      <c r="H12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" customHeight="1" ht="37.5">
-      <c r="A13"/>
+      <c r="H12" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
       <c r="E13"/>
-      <c r="H13"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14"/>
-      <c r="H14" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15"/>
-      <c r="H15" t="s">
-        <v>41</v>
+      <c r="H13" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -777,9 +671,15 @@
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="I9:I9"/>
-    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="I7:I7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="H10:J10"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="H11:J11"/>
@@ -789,12 +689,6 @@
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="H13:J13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="H15:J15"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
